--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -8,20 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dratw\Documents\codes\priceChecker\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD28FC3-B2FD-4E97-AF31-CF5D5E819EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1290B2E0-25EF-4010-91E2-7BDD94B2C693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="850" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
-    <sheet name="hold" sheetId="2" r:id="rId2"/>
+    <sheet name="flip" sheetId="4" r:id="rId2"/>
+    <sheet name="hold" sheetId="2" r:id="rId3"/>
+    <sheet name="expected1" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="148">
   <si>
     <t>Product_name</t>
   </si>
@@ -47,52 +62,424 @@
     <t>Additional_sites</t>
   </si>
   <si>
-    <t>UGG Classic Ultra Mini Platform Driftwood (W)</t>
-  </si>
-  <si>
-    <t>1135092-DRI</t>
+    <t>adidas Yeezy Slide Flax</t>
+  </si>
+  <si>
+    <t>FZ5896</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>340,0</t>
+  </si>
+  <si>
+    <t>320,0</t>
+  </si>
+  <si>
+    <t>StockX</t>
+  </si>
+  <si>
+    <t>adidas Yeezy Slide Resin (2022)</t>
+  </si>
+  <si>
+    <t>FZ5904</t>
+  </si>
+  <si>
+    <t>360,0</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>350,0</t>
+  </si>
+  <si>
+    <t>Jordan 1 Low Aluminum (W)</t>
+  </si>
+  <si>
+    <t>DC0774-141</t>
   </si>
   <si>
     <t>7W</t>
   </si>
   <si>
+    <t>610,0</t>
+  </si>
+  <si>
+    <t>620,0</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Hypeboost/Sneakit/</t>
+  </si>
+  <si>
+    <t>Jordan 1 Mid White Metallic Gold Obsidian</t>
+  </si>
+  <si>
+    <t>554724-174</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>530,0</t>
+  </si>
+  <si>
+    <t>StockX/Alias</t>
+  </si>
+  <si>
+    <t>Restocks/Klekt/Hypeboost/Sneakit/</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>550,0</t>
+  </si>
+  <si>
+    <t>510,0</t>
+  </si>
+  <si>
+    <t>Restocks/Hypeboost/Sneakit/</t>
+  </si>
+  <si>
+    <t>490,0</t>
+  </si>
+  <si>
+    <t>Jordan 1 Retro High OG Gorge Green</t>
+  </si>
+  <si>
+    <t>DZ5485-303</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>980,0</t>
+  </si>
+  <si>
+    <t>1120,0</t>
+  </si>
+  <si>
+    <t>Jordan 11 Retro Cherry (2022)</t>
+  </si>
+  <si>
+    <t>CT8012-116</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>880,0</t>
+  </si>
+  <si>
+    <t>990,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk High Panda Black White (2021)</t>
+  </si>
+  <si>
+    <t>DD1399-105</t>
+  </si>
+  <si>
+    <t>560,0</t>
+  </si>
+  <si>
+    <t>Sneakit/</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Dark Driftwood (W)</t>
+  </si>
+  <si>
+    <t>DD1503-200</t>
+  </si>
+  <si>
+    <t>10.5W</t>
+  </si>
+  <si>
+    <t>480,0</t>
+  </si>
+  <si>
+    <t>Hypeboost/</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Disrupt 2 Panda (W)</t>
+  </si>
+  <si>
+    <t>DV4024-002</t>
+  </si>
+  <si>
+    <t>6.5W</t>
+  </si>
+  <si>
+    <t>540,0</t>
+  </si>
+  <si>
+    <t>Klekt/Hypeboost/Sneakit/</t>
+  </si>
+  <si>
+    <t>9.5W</t>
+  </si>
+  <si>
+    <t>Restocks/Klekt/Hypeboost/</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Grey Fog</t>
+  </si>
+  <si>
+    <t>DD1391-103</t>
+  </si>
+  <si>
+    <t>810,0</t>
+  </si>
+  <si>
+    <t>1030,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Light Iron Ore (W)</t>
+  </si>
+  <si>
+    <t>DQ7576-001</t>
+  </si>
+  <si>
+    <t>9W</t>
+  </si>
+  <si>
+    <t>460,0</t>
+  </si>
+  <si>
+    <t>570,0</t>
+  </si>
+  <si>
+    <t>470,0</t>
+  </si>
+  <si>
+    <t>520,0</t>
+  </si>
+  <si>
+    <t>10W</t>
+  </si>
+  <si>
+    <t>580,0</t>
+  </si>
+  <si>
+    <t>11W</t>
+  </si>
+  <si>
+    <t>650,0</t>
+  </si>
+  <si>
+    <t>720,0</t>
+  </si>
+  <si>
+    <t>12W</t>
+  </si>
+  <si>
+    <t>730,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Next Nature White Black Panda (W)</t>
+  </si>
+  <si>
+    <t>DD1873-102</t>
+  </si>
+  <si>
+    <t>6W</t>
+  </si>
+  <si>
+    <t>Restocks/</t>
+  </si>
+  <si>
+    <t>7.5W</t>
+  </si>
+  <si>
+    <t>8W</t>
+  </si>
+  <si>
+    <t>600,0</t>
+  </si>
+  <si>
+    <t>590,0</t>
+  </si>
+  <si>
+    <t>8.5W</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Next Nature White Mint (W)</t>
+  </si>
+  <si>
+    <t>DN1431-102</t>
+  </si>
+  <si>
+    <t>450,0</t>
+  </si>
+  <si>
+    <t>430,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Retro White Black Panda (2021) (GS)</t>
+  </si>
+  <si>
+    <t>CW1590-100</t>
+  </si>
+  <si>
+    <t>6Y</t>
+  </si>
+  <si>
+    <t>Restocks/Sneakit/</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Retro White Black Panda (2021) (W)</t>
+  </si>
+  <si>
+    <t>DD1503-101</t>
+  </si>
+  <si>
+    <t>640,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low SE 85 Double Swoosh Sail Orange (W)</t>
+  </si>
+  <si>
+    <t>DO9457-100</t>
+  </si>
+  <si>
+    <t>500,0</t>
+  </si>
+  <si>
     <t>700,0</t>
   </si>
   <si>
-    <t>-60,0</t>
-  </si>
-  <si>
-    <t>StockX</t>
-  </si>
-  <si>
-    <t>adidas Yeezy Slide Flax</t>
-  </si>
-  <si>
-    <t>FZ5896</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>350,0</t>
-  </si>
-  <si>
-    <t>320,0</t>
+    <t>Nike Dunk Low Triple White (2021) (W)</t>
+  </si>
+  <si>
+    <t>DD1503-109</t>
+  </si>
+  <si>
+    <t>420,0</t>
+  </si>
+  <si>
+    <t>400,0</t>
+  </si>
+  <si>
+    <t>Klekt/Sneakit/</t>
+  </si>
+  <si>
+    <t>‌ ‌</t>
+  </si>
+  <si>
+    <t>380,0</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low UCLA</t>
+  </si>
+  <si>
+    <t>DD1391-402</t>
+  </si>
+  <si>
+    <t>440,0</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>New Balance 550 White Grey</t>
+  </si>
+  <si>
+    <t>BB550PB1</t>
+  </si>
+  <si>
+    <t>adidas Handball Spezial Navy Gum</t>
+  </si>
+  <si>
+    <t>BD7633</t>
+  </si>
+  <si>
+    <t>390,0</t>
+  </si>
+  <si>
+    <t>Restocks/Klekt/Wethenew/Hypeboost/</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>HP6772</t>
+  </si>
+  <si>
+    <t>adidas Forum Low The Grinch</t>
+  </si>
+  <si>
+    <t>630,0</t>
+  </si>
+  <si>
+    <t>11.5W</t>
+  </si>
+  <si>
+    <t>DZ4706-200</t>
   </si>
   <si>
     <t>Nike Dunk Low Terry Swoosh (W)</t>
   </si>
   <si>
-    <t>DZ4706-200</t>
-  </si>
-  <si>
-    <t>10W</t>
-  </si>
-  <si>
-    <t>500,0</t>
-  </si>
-  <si>
-    <t>450,0</t>
+    <t>DN3866-100</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Safari Mix (W)</t>
+  </si>
+  <si>
+    <t>7Y</t>
+  </si>
+  <si>
+    <t>DX3382-400</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Next Nature Homer Simpson (GS)</t>
+  </si>
+  <si>
+    <t>680,0</t>
+  </si>
+  <si>
+    <t>DD1399-106</t>
+  </si>
+  <si>
+    <t>Nike Dunk High Championship White Red</t>
+  </si>
+  <si>
+    <t>670,0</t>
+  </si>
+  <si>
+    <t>7C</t>
+  </si>
+  <si>
+    <t>DO5441-001</t>
+  </si>
+  <si>
+    <t>Jordan 1 Retro Low OG SP Travis Scott Black Phantom (TD)</t>
+  </si>
+  <si>
+    <t>890,0</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>553558-371</t>
+  </si>
+  <si>
+    <t>Jordan 1 Low Green Toe</t>
+  </si>
+  <si>
+    <t>553558-612</t>
+  </si>
+  <si>
+    <t>Jordan 1 Low Bred Toe</t>
+  </si>
+  <si>
+    <t>660,0</t>
   </si>
 </sst>
 </file>
@@ -463,19 +850,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08979D0F-36D2-4431-A9C1-4925DA822542}">
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -509,25 +888,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>147</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -535,25 +917,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>87</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -561,25 +946,5110 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>19</v>
       </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I149"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" t="s">
+        <v>70</v>
+      </c>
+      <c r="F41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" t="s">
+        <v>71</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" t="s">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" t="s">
+        <v>77</v>
+      </c>
+      <c r="F58" t="s">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" t="s">
+        <v>77</v>
+      </c>
+      <c r="F59" t="s">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+      <c r="F60" t="s">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" t="s">
+        <v>77</v>
+      </c>
+      <c r="F61" t="s">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" t="s">
+        <v>77</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" t="s">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" t="s">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" t="s">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" t="s">
+        <v>71</v>
+      </c>
+      <c r="F68" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" t="s">
+        <v>71</v>
+      </c>
+      <c r="F69" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
+        <v>71</v>
+      </c>
+      <c r="I69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" t="s">
+        <v>71</v>
+      </c>
+      <c r="F70" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>49</v>
+      </c>
+      <c r="F71" t="s">
+        <v>71</v>
+      </c>
+      <c r="G71" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" t="s">
+        <v>71</v>
+      </c>
+      <c r="G72" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" t="s">
+        <v>49</v>
+      </c>
+      <c r="F73" t="s">
+        <v>71</v>
+      </c>
+      <c r="G73" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E74" t="s">
+        <v>49</v>
+      </c>
+      <c r="F74" t="s">
+        <v>71</v>
+      </c>
+      <c r="G74" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" t="s">
+        <v>71</v>
+      </c>
+      <c r="G75" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" t="s">
+        <v>49</v>
+      </c>
+      <c r="F76" t="s">
+        <v>71</v>
+      </c>
+      <c r="G76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77" t="s">
+        <v>85</v>
+      </c>
+      <c r="E77" t="s">
+        <v>49</v>
+      </c>
+      <c r="F77" t="s">
+        <v>71</v>
+      </c>
+      <c r="G77" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" t="s">
+        <v>82</v>
+      </c>
+      <c r="D78" t="s">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>49</v>
+      </c>
+      <c r="F78" t="s">
+        <v>71</v>
+      </c>
+      <c r="G78" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" t="s">
+        <v>85</v>
+      </c>
+      <c r="E79" t="s">
+        <v>49</v>
+      </c>
+      <c r="F79" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" t="s">
+        <v>85</v>
+      </c>
+      <c r="E80" t="s">
+        <v>49</v>
+      </c>
+      <c r="F80" t="s">
+        <v>71</v>
+      </c>
+      <c r="G80" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" t="s">
+        <v>85</v>
+      </c>
+      <c r="E81" t="s">
+        <v>49</v>
+      </c>
+      <c r="F81" t="s">
+        <v>71</v>
+      </c>
+      <c r="G81" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" t="s">
+        <v>71</v>
+      </c>
+      <c r="G82" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" t="s">
+        <v>85</v>
+      </c>
+      <c r="E83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F83" t="s">
+        <v>71</v>
+      </c>
+      <c r="G83" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E84" t="s">
+        <v>49</v>
+      </c>
+      <c r="F84" t="s">
+        <v>71</v>
+      </c>
+      <c r="G84" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" t="s">
+        <v>85</v>
+      </c>
+      <c r="E85" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85" t="s">
+        <v>71</v>
+      </c>
+      <c r="G85" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" t="s">
+        <v>85</v>
+      </c>
+      <c r="E86" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" t="s">
+        <v>85</v>
+      </c>
+      <c r="E87" t="s">
+        <v>49</v>
+      </c>
+      <c r="F87" t="s">
+        <v>71</v>
+      </c>
+      <c r="G87" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
+        <v>85</v>
+      </c>
+      <c r="E88" t="s">
+        <v>49</v>
+      </c>
+      <c r="F88" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" t="s">
+        <v>85</v>
+      </c>
+      <c r="E89" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" t="s">
+        <v>71</v>
+      </c>
+      <c r="G89" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" t="s">
+        <v>49</v>
+      </c>
+      <c r="F90" t="s">
+        <v>71</v>
+      </c>
+      <c r="G90" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" t="s">
+        <v>85</v>
+      </c>
+      <c r="E91" t="s">
+        <v>49</v>
+      </c>
+      <c r="F91" t="s">
+        <v>71</v>
+      </c>
+      <c r="G91" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" t="s">
+        <v>85</v>
+      </c>
+      <c r="E92" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" t="s">
+        <v>71</v>
+      </c>
+      <c r="G92" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" t="s">
+        <v>85</v>
+      </c>
+      <c r="E93" t="s">
+        <v>49</v>
+      </c>
+      <c r="F93" t="s">
+        <v>71</v>
+      </c>
+      <c r="G93" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>81</v>
+      </c>
+      <c r="C94" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" t="s">
+        <v>85</v>
+      </c>
+      <c r="E94" t="s">
+        <v>49</v>
+      </c>
+      <c r="F94" t="s">
+        <v>71</v>
+      </c>
+      <c r="G94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" t="s">
+        <v>85</v>
+      </c>
+      <c r="E95" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" t="s">
+        <v>71</v>
+      </c>
+      <c r="G95" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C96" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" t="s">
+        <v>86</v>
+      </c>
+      <c r="E96" t="s">
+        <v>87</v>
+      </c>
+      <c r="F96" t="s">
+        <v>88</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97" t="s">
+        <v>87</v>
+      </c>
+      <c r="F97" t="s">
+        <v>88</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" t="s">
+        <v>82</v>
+      </c>
+      <c r="D98" t="s">
+        <v>86</v>
+      </c>
+      <c r="E98" t="s">
+        <v>87</v>
+      </c>
+      <c r="F98" t="s">
+        <v>88</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>81</v>
+      </c>
+      <c r="C99" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" t="s">
+        <v>86</v>
+      </c>
+      <c r="E99" t="s">
+        <v>87</v>
+      </c>
+      <c r="F99" t="s">
+        <v>88</v>
+      </c>
+      <c r="G99" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>81</v>
+      </c>
+      <c r="C100" t="s">
+        <v>82</v>
+      </c>
+      <c r="D100" t="s">
+        <v>86</v>
+      </c>
+      <c r="E100" t="s">
+        <v>87</v>
+      </c>
+      <c r="F100" t="s">
+        <v>88</v>
+      </c>
+      <c r="G100" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>81</v>
+      </c>
+      <c r="C101" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101" t="s">
+        <v>89</v>
+      </c>
+      <c r="E101" t="s">
+        <v>75</v>
+      </c>
+      <c r="F101" t="s">
+        <v>75</v>
+      </c>
+      <c r="G101" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>81</v>
+      </c>
+      <c r="C102" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102" t="s">
+        <v>75</v>
+      </c>
+      <c r="F102" t="s">
+        <v>75</v>
+      </c>
+      <c r="G102" t="s">
+        <v>30</v>
+      </c>
+      <c r="H102" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="B103" t="s">
+        <v>81</v>
+      </c>
+      <c r="C103" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" t="s">
+        <v>89</v>
+      </c>
+      <c r="E103" t="s">
+        <v>75</v>
+      </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s">
+        <v>30</v>
+      </c>
+      <c r="H103" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>102</v>
+      </c>
+      <c r="B104" t="s">
+        <v>81</v>
+      </c>
+      <c r="C104" t="s">
+        <v>82</v>
+      </c>
+      <c r="D104" t="s">
+        <v>89</v>
+      </c>
+      <c r="E104" t="s">
+        <v>75</v>
+      </c>
+      <c r="F104" t="s">
+        <v>75</v>
+      </c>
+      <c r="G104" t="s">
+        <v>30</v>
+      </c>
+      <c r="H104" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>103</v>
+      </c>
+      <c r="B105" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" t="s">
+        <v>89</v>
+      </c>
+      <c r="E105" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" t="s">
+        <v>75</v>
+      </c>
+      <c r="G105" t="s">
+        <v>30</v>
+      </c>
+      <c r="H105" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="B106" t="s">
+        <v>81</v>
+      </c>
+      <c r="C106" t="s">
+        <v>82</v>
+      </c>
+      <c r="D106" t="s">
+        <v>89</v>
+      </c>
+      <c r="E106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F106" t="s">
+        <v>75</v>
+      </c>
+      <c r="G106" t="s">
+        <v>30</v>
+      </c>
+      <c r="H106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>105</v>
+      </c>
+      <c r="B107" t="s">
+        <v>81</v>
+      </c>
+      <c r="C107" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" t="s">
+        <v>89</v>
+      </c>
+      <c r="E107" t="s">
+        <v>75</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="G107" t="s">
+        <v>30</v>
+      </c>
+      <c r="H107" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>106</v>
+      </c>
+      <c r="B108" t="s">
+        <v>81</v>
+      </c>
+      <c r="C108" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108" t="s">
+        <v>89</v>
+      </c>
+      <c r="E108" t="s">
+        <v>75</v>
+      </c>
+      <c r="F108" t="s">
+        <v>75</v>
+      </c>
+      <c r="G108" t="s">
+        <v>30</v>
+      </c>
+      <c r="H108" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
+        <v>81</v>
+      </c>
+      <c r="C109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D109" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109" t="s">
+        <v>36</v>
+      </c>
+      <c r="F109" t="s">
+        <v>75</v>
+      </c>
+      <c r="G109" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" t="s">
+        <v>75</v>
+      </c>
+      <c r="I109" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="B110" t="s">
+        <v>90</v>
+      </c>
+      <c r="C110" t="s">
+        <v>91</v>
+      </c>
+      <c r="D110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E110" t="s">
+        <v>54</v>
+      </c>
+      <c r="F110" t="s">
+        <v>70</v>
+      </c>
+      <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>109</v>
+      </c>
+      <c r="B111" t="s">
+        <v>90</v>
+      </c>
+      <c r="C111" t="s">
+        <v>91</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+      <c r="E111" t="s">
+        <v>92</v>
+      </c>
+      <c r="F111" t="s">
+        <v>70</v>
+      </c>
+      <c r="G111" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="B112" t="s">
+        <v>90</v>
+      </c>
+      <c r="C112" t="s">
+        <v>91</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" t="s">
+        <v>92</v>
+      </c>
+      <c r="F112" t="s">
+        <v>70</v>
+      </c>
+      <c r="G112" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
+        <v>90</v>
+      </c>
+      <c r="C113" t="s">
+        <v>91</v>
+      </c>
+      <c r="D113" t="s">
+        <v>58</v>
+      </c>
+      <c r="E113" t="s">
+        <v>92</v>
+      </c>
+      <c r="F113" t="s">
+        <v>70</v>
+      </c>
+      <c r="G113" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>112</v>
+      </c>
+      <c r="B114" t="s">
+        <v>90</v>
+      </c>
+      <c r="C114" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" t="s">
+        <v>70</v>
+      </c>
+      <c r="G114" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="B115" t="s">
+        <v>90</v>
+      </c>
+      <c r="C115" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" t="s">
+        <v>85</v>
+      </c>
+      <c r="E115" t="s">
+        <v>92</v>
+      </c>
+      <c r="F115" t="s">
+        <v>72</v>
+      </c>
+      <c r="G115" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>114</v>
+      </c>
+      <c r="B116" t="s">
+        <v>90</v>
+      </c>
+      <c r="C116" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" t="s">
+        <v>89</v>
+      </c>
+      <c r="E116" t="s">
+        <v>54</v>
+      </c>
+      <c r="F116" t="s">
+        <v>72</v>
+      </c>
+      <c r="G116" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s">
+        <v>90</v>
+      </c>
+      <c r="C117" t="s">
+        <v>91</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" t="s">
+        <v>92</v>
+      </c>
+      <c r="F117" t="s">
+        <v>72</v>
+      </c>
+      <c r="G117" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>116</v>
+      </c>
+      <c r="B118" t="s">
+        <v>94</v>
+      </c>
+      <c r="C118" t="s">
+        <v>95</v>
+      </c>
+      <c r="D118" t="s">
+        <v>96</v>
+      </c>
+      <c r="E118" t="s">
+        <v>34</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" t="s">
+        <v>33</v>
+      </c>
+      <c r="I118" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
+        <v>98</v>
+      </c>
+      <c r="C119" t="s">
+        <v>99</v>
+      </c>
+      <c r="D119" t="s">
+        <v>86</v>
+      </c>
+      <c r="E119" t="s">
+        <v>87</v>
+      </c>
+      <c r="F119" t="s">
+        <v>100</v>
+      </c>
+      <c r="G119" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>98</v>
+      </c>
+      <c r="C120" t="s">
+        <v>99</v>
+      </c>
+      <c r="D120" t="s">
+        <v>86</v>
+      </c>
+      <c r="E120" t="s">
+        <v>87</v>
+      </c>
+      <c r="F120" t="s">
+        <v>100</v>
+      </c>
+      <c r="G120" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>101</v>
+      </c>
+      <c r="C121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D121" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121" t="s">
+        <v>29</v>
+      </c>
+      <c r="F121" t="s">
+        <v>29</v>
+      </c>
+      <c r="G121" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" t="s">
+        <v>29</v>
+      </c>
+      <c r="I121" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D122" t="s">
+        <v>89</v>
+      </c>
+      <c r="E122" t="s">
+        <v>103</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" t="s">
+        <v>33</v>
+      </c>
+      <c r="I122" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" t="s">
+        <v>102</v>
+      </c>
+      <c r="D123" t="s">
+        <v>89</v>
+      </c>
+      <c r="E123" t="s">
+        <v>103</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" t="s">
+        <v>33</v>
+      </c>
+      <c r="I123" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>101</v>
+      </c>
+      <c r="C124" t="s">
+        <v>102</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" t="s">
+        <v>49</v>
+      </c>
+      <c r="F124" t="s">
+        <v>59</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" t="s">
+        <v>49</v>
+      </c>
+      <c r="I124" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" t="s">
+        <v>102</v>
+      </c>
+      <c r="D125" t="s">
+        <v>74</v>
+      </c>
+      <c r="E125" t="s">
+        <v>104</v>
+      </c>
+      <c r="F125" t="s">
+        <v>88</v>
+      </c>
+      <c r="G125" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" t="s">
+        <v>104</v>
+      </c>
+      <c r="I125" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>105</v>
+      </c>
+      <c r="C126" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" t="s">
+        <v>58</v>
+      </c>
+      <c r="E126" t="s">
+        <v>107</v>
+      </c>
+      <c r="F126" t="s">
+        <v>108</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" t="s">
+        <v>107</v>
+      </c>
+      <c r="I126" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>105</v>
+      </c>
+      <c r="C127" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127" t="s">
+        <v>58</v>
+      </c>
+      <c r="E127" t="s">
+        <v>107</v>
+      </c>
+      <c r="F127" t="s">
+        <v>108</v>
+      </c>
+      <c r="G127" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" t="s">
+        <v>107</v>
+      </c>
+      <c r="I127" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>105</v>
+      </c>
+      <c r="C128" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128" t="s">
+        <v>58</v>
+      </c>
+      <c r="E128" t="s">
+        <v>107</v>
+      </c>
+      <c r="F128" t="s">
+        <v>108</v>
+      </c>
+      <c r="G128" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" t="s">
+        <v>107</v>
+      </c>
+      <c r="I128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>105</v>
+      </c>
+      <c r="C129" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" t="s">
+        <v>58</v>
+      </c>
+      <c r="E129" t="s">
+        <v>107</v>
+      </c>
+      <c r="F129" t="s">
+        <v>108</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" t="s">
+        <v>107</v>
+      </c>
+      <c r="I129" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>105</v>
+      </c>
+      <c r="C130" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" t="s">
+        <v>58</v>
+      </c>
+      <c r="E130" t="s">
+        <v>107</v>
+      </c>
+      <c r="F130" t="s">
+        <v>108</v>
+      </c>
+      <c r="G130" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" t="s">
+        <v>107</v>
+      </c>
+      <c r="I130" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>105</v>
+      </c>
+      <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" t="s">
+        <v>58</v>
+      </c>
+      <c r="E131" t="s">
+        <v>107</v>
+      </c>
+      <c r="F131" t="s">
+        <v>108</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" t="s">
+        <v>107</v>
+      </c>
+      <c r="I131" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
+        <v>105</v>
+      </c>
+      <c r="C132" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" t="s">
+        <v>58</v>
+      </c>
+      <c r="E132" t="s">
+        <v>107</v>
+      </c>
+      <c r="F132" t="s">
+        <v>108</v>
+      </c>
+      <c r="G132" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="s">
+        <v>107</v>
+      </c>
+      <c r="I132" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>131</v>
+      </c>
+      <c r="B133" t="s">
+        <v>105</v>
+      </c>
+      <c r="C133" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" t="s">
+        <v>58</v>
+      </c>
+      <c r="E133" t="s">
+        <v>107</v>
+      </c>
+      <c r="F133" t="s">
+        <v>108</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="s">
+        <v>107</v>
+      </c>
+      <c r="I133" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>132</v>
+      </c>
+      <c r="B134" t="s">
+        <v>110</v>
+      </c>
+      <c r="C134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" t="s">
+        <v>85</v>
+      </c>
+      <c r="E134" t="s">
+        <v>107</v>
+      </c>
+      <c r="F134" t="s">
+        <v>111</v>
+      </c>
+      <c r="G134" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" t="s">
+        <v>107</v>
+      </c>
+      <c r="I134" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>112</v>
+      </c>
+      <c r="C135" t="s">
+        <v>113</v>
+      </c>
+      <c r="D135" t="s">
+        <v>32</v>
+      </c>
+      <c r="E135" t="s">
+        <v>70</v>
+      </c>
+      <c r="F135" t="s">
+        <v>114</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>112</v>
+      </c>
+      <c r="C136" t="s">
+        <v>113</v>
+      </c>
+      <c r="D136" t="s">
+        <v>32</v>
+      </c>
+      <c r="E136" t="s">
+        <v>70</v>
+      </c>
+      <c r="F136" t="s">
+        <v>114</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>135</v>
+      </c>
+      <c r="B137" t="s">
+        <v>112</v>
+      </c>
+      <c r="C137" t="s">
+        <v>113</v>
+      </c>
+      <c r="D137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E137" t="s">
+        <v>70</v>
+      </c>
+      <c r="F137" t="s">
+        <v>114</v>
+      </c>
+      <c r="G137" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>136</v>
+      </c>
+      <c r="B138" t="s">
+        <v>112</v>
+      </c>
+      <c r="C138" t="s">
+        <v>113</v>
+      </c>
+      <c r="D138" t="s">
+        <v>32</v>
+      </c>
+      <c r="E138" t="s">
+        <v>70</v>
+      </c>
+      <c r="F138" t="s">
+        <v>114</v>
+      </c>
+      <c r="G138" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>112</v>
+      </c>
+      <c r="C139" t="s">
+        <v>113</v>
+      </c>
+      <c r="D139" t="s">
+        <v>32</v>
+      </c>
+      <c r="E139" t="s">
+        <v>70</v>
+      </c>
+      <c r="F139" t="s">
+        <v>114</v>
+      </c>
+      <c r="G139" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>138</v>
+      </c>
+      <c r="B140" t="s">
+        <v>112</v>
+      </c>
+      <c r="C140" t="s">
+        <v>113</v>
+      </c>
+      <c r="D140" t="s">
+        <v>32</v>
+      </c>
+      <c r="E140" t="s">
+        <v>70</v>
+      </c>
+      <c r="F140" t="s">
+        <v>114</v>
+      </c>
+      <c r="G140" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>139</v>
+      </c>
+      <c r="B141" t="s">
+        <v>112</v>
+      </c>
+      <c r="C141" t="s">
+        <v>113</v>
+      </c>
+      <c r="D141" t="s">
+        <v>32</v>
+      </c>
+      <c r="E141" t="s">
+        <v>70</v>
+      </c>
+      <c r="F141" t="s">
+        <v>114</v>
+      </c>
+      <c r="G141" t="s">
+        <v>13</v>
+      </c>
+      <c r="H141" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>140</v>
+      </c>
+      <c r="B142" t="s">
+        <v>112</v>
+      </c>
+      <c r="C142" t="s">
+        <v>113</v>
+      </c>
+      <c r="D142" t="s">
+        <v>32</v>
+      </c>
+      <c r="E142" t="s">
+        <v>70</v>
+      </c>
+      <c r="F142" t="s">
+        <v>114</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>141</v>
+      </c>
+      <c r="B143" t="s">
+        <v>112</v>
+      </c>
+      <c r="C143" t="s">
+        <v>113</v>
+      </c>
+      <c r="D143" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143" t="s">
+        <v>70</v>
+      </c>
+      <c r="F143" t="s">
+        <v>114</v>
+      </c>
+      <c r="G143" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
+        <v>112</v>
+      </c>
+      <c r="C144" t="s">
+        <v>113</v>
+      </c>
+      <c r="D144" t="s">
+        <v>32</v>
+      </c>
+      <c r="E144" t="s">
+        <v>70</v>
+      </c>
+      <c r="F144" t="s">
+        <v>114</v>
+      </c>
+      <c r="G144" t="s">
+        <v>13</v>
+      </c>
+      <c r="H144" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>143</v>
+      </c>
+      <c r="B145" t="s">
+        <v>112</v>
+      </c>
+      <c r="C145" t="s">
+        <v>113</v>
+      </c>
+      <c r="D145" t="s">
+        <v>32</v>
+      </c>
+      <c r="E145" t="s">
+        <v>70</v>
+      </c>
+      <c r="F145" t="s">
+        <v>114</v>
+      </c>
+      <c r="G145" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>144</v>
+      </c>
+      <c r="B146" t="s">
+        <v>112</v>
+      </c>
+      <c r="C146" t="s">
+        <v>113</v>
+      </c>
+      <c r="D146" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" t="s">
+        <v>72</v>
+      </c>
+      <c r="F146" t="s">
+        <v>54</v>
+      </c>
+      <c r="G146" t="s">
+        <v>24</v>
+      </c>
+      <c r="H146" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>145</v>
+      </c>
+      <c r="B147" t="s">
+        <v>112</v>
+      </c>
+      <c r="C147" t="s">
+        <v>113</v>
+      </c>
+      <c r="D147" t="s">
+        <v>115</v>
+      </c>
+      <c r="E147" t="s">
+        <v>103</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="G147" t="s">
+        <v>24</v>
+      </c>
+      <c r="H147" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>146</v>
+      </c>
+      <c r="B148" t="s">
+        <v>116</v>
+      </c>
+      <c r="C148" t="s">
+        <v>117</v>
+      </c>
+      <c r="D148" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148" t="s">
+        <v>34</v>
+      </c>
+      <c r="F148" t="s">
+        <v>92</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>147</v>
+      </c>
+      <c r="B149" t="s">
+        <v>116</v>
+      </c>
+      <c r="C149" t="s">
+        <v>117</v>
+      </c>
+      <c r="D149" t="s">
+        <v>28</v>
+      </c>
+      <c r="E149" t="s">
+        <v>34</v>
+      </c>
+      <c r="F149" t="s">
+        <v>92</v>
+      </c>
+      <c r="G149" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
